--- a/backend/data/site-sheets/PROMAX.xlsx
+++ b/backend/data/site-sheets/PROMAX.xlsx
@@ -789,7 +789,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -817,7 +817,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="E3" t="n">
